--- a/diurenmw/Excels/SkillObj_技能表.xlsx
+++ b/diurenmw/Excels/SkillObj_技能表.xlsx
@@ -133,6 +133,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>关联武器种类：</t>
     </r>
     <r>
@@ -359,7 +365,7 @@
     </r>
   </si>
   <si>
-    <t>100|100|150</t>
+    <t>30|30|40</t>
   </si>
   <si>
     <r>
@@ -455,7 +461,7 @@
     <t>旋风斩</t>
   </si>
   <si>
-    <t>450|450|450|450|450</t>
+    <t>170|170|170|170</t>
   </si>
   <si>
     <r>
@@ -593,7 +599,7 @@
     <t>暴风雪</t>
   </si>
   <si>
-    <t>170|170|170</t>
+    <t>70|70|70</t>
   </si>
   <si>
     <t>改变指定地区环境，降下3s的暴风雪，对区域内敌人持续造成伤害并减速敌人。</t>
@@ -608,7 +614,7 @@
     <t>万雷引</t>
   </si>
   <si>
-    <t>210|210|210|210|210</t>
+    <t>75|75|75|75|75</t>
   </si>
   <si>
     <t>在指定怪物身上种下雷核，持续牵引周围怪物5s并对周围所有敌人造成伤害。</t>
@@ -623,7 +629,7 @@
     <t>陨石术</t>
   </si>
   <si>
-    <t>1600|200|200|200</t>
+    <t>420|100|100|100</t>
   </si>
   <si>
     <t>以法杖牵引召来天外陨石，砸向指定地点。陨石落地造成伤害，之后会在地面形成3s岩浆区域，持续造成伤害。</t>
@@ -664,7 +670,7 @@
     <t>冰封万里</t>
   </si>
   <si>
-    <t>2000|5500</t>
+    <t>500|2300</t>
   </si>
   <si>
     <t>向冰雪之神借力，瞬间冻结大范围内的所有敌人，在每个敌人头顶凝成一只冰矛重重砸下，造成高额伤害并破冰。</t>
@@ -673,7 +679,7 @@
     <t>雷神之怒</t>
   </si>
   <si>
-    <t>300|800</t>
+    <t>100|300</t>
   </si>
   <si>
     <t>向雷电之神借力，召唤出一朵20s的雷云，持续攻击周围敌人。每次释放技能，雷云释放一次高伤雷击。</t>
@@ -2061,7 +2067,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr defaultColWidth="7.46666666666667" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.6814814814815" style="1" customWidth="1"/>
@@ -2232,7 +2238,7 @@
         <v>20</v>
       </c>
       <c r="I6" s="3">
-        <v>330</v>
+        <v>120</v>
       </c>
       <c r="J6" s="18" t="s">
         <v>28</v>
@@ -2264,7 +2270,7 @@
         <v>20</v>
       </c>
       <c r="I7" s="3">
-        <v>470</v>
+        <v>140</v>
       </c>
       <c r="J7" s="19" t="s">
         <v>30</v>
@@ -2296,7 +2302,7 @@
         <v>20</v>
       </c>
       <c r="I8" s="3">
-        <v>200</v>
+        <v>70</v>
       </c>
       <c r="J8" s="19" t="s">
         <v>32</v>
@@ -2328,7 +2334,7 @@
         <v>30</v>
       </c>
       <c r="I9" s="3">
-        <v>800</v>
+        <v>330</v>
       </c>
       <c r="J9" s="19" t="s">
         <v>34</v>
@@ -2360,7 +2366,7 @@
         <v>25</v>
       </c>
       <c r="I10" s="3">
-        <v>700</v>
+        <v>260</v>
       </c>
       <c r="J10" s="18" t="s">
         <v>36</v>
@@ -2392,7 +2398,7 @@
         <v>40</v>
       </c>
       <c r="I11" s="3">
-        <v>1700</v>
+        <v>480</v>
       </c>
       <c r="J11" s="18" t="s">
         <v>38</v>
@@ -2456,7 +2462,7 @@
         <v>55</v>
       </c>
       <c r="I13" s="3">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="J13" s="20" t="s">
         <v>43</v>
@@ -2517,50 +2523,22 @@
         <v>75</v>
       </c>
       <c r="I15" s="3">
-        <v>8000</v>
+        <v>2600</v>
       </c>
       <c r="J15" s="19" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="1">
-        <v>1012</v>
-      </c>
-      <c r="B16" s="13" t="s">
+    <row r="16" spans="2:10">
+      <c r="B16" s="13"/>
+      <c r="J16" s="21"/>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="1">
+        <v>2001</v>
+      </c>
+      <c r="B17" s="13" t="s">
         <v>48</v>
-      </c>
-      <c r="C16" s="1">
-        <v>1</v>
-      </c>
-      <c r="D16" s="1">
-        <v>2</v>
-      </c>
-      <c r="E16" s="1">
-        <v>1</v>
-      </c>
-      <c r="F16" s="3">
-        <v>163644</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0</v>
-      </c>
-      <c r="H16" s="1">
-        <v>0</v>
-      </c>
-      <c r="I16" s="3">
-        <v>220</v>
-      </c>
-      <c r="J16" s="21" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="11">
-        <v>1013</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>50</v>
       </c>
       <c r="C17" s="1">
         <v>1</v>
@@ -2572,27 +2550,27 @@
         <v>1</v>
       </c>
       <c r="F17" s="3">
-        <v>163638</v>
+        <v>163644</v>
       </c>
       <c r="G17" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I17" s="3">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="J17" s="21" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="1">
-        <v>1014</v>
+      <c r="A18" s="11">
+        <v>2002</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C18" s="1">
         <v>1</v>
@@ -2604,27 +2582,27 @@
         <v>1</v>
       </c>
       <c r="F18" s="3">
-        <v>163680</v>
+        <v>163638</v>
       </c>
       <c r="G18" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H18" s="1">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I18" s="3">
-        <v>420</v>
+        <v>110</v>
       </c>
       <c r="J18" s="21" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="11">
-        <v>1015</v>
+      <c r="A19" s="1">
+        <v>2003</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C19" s="1">
         <v>1</v>
@@ -2636,27 +2614,27 @@
         <v>1</v>
       </c>
       <c r="F19" s="3">
-        <v>163642</v>
+        <v>163680</v>
       </c>
       <c r="G19" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H19" s="1">
-        <v>35</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>55</v>
+        <v>25</v>
+      </c>
+      <c r="I19" s="3">
+        <v>150</v>
       </c>
       <c r="J19" s="21" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="1">
-        <v>1016</v>
+      <c r="A20" s="11">
+        <v>2004</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C20" s="1">
         <v>1</v>
@@ -2668,27 +2646,27 @@
         <v>1</v>
       </c>
       <c r="F20" s="3">
-        <v>143723</v>
+        <v>163642</v>
       </c>
       <c r="G20" s="1">
         <v>7</v>
       </c>
       <c r="H20" s="1">
-        <v>30</v>
-      </c>
-      <c r="I20" s="3">
-        <v>580</v>
-      </c>
-      <c r="J20" s="22" t="s">
-        <v>58</v>
+        <v>35</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="J20" s="21" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="11">
-        <v>1017</v>
+      <c r="A21" s="1">
+        <v>2005</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C21" s="1">
         <v>1</v>
@@ -2700,27 +2678,27 @@
         <v>1</v>
       </c>
       <c r="F21" s="3">
-        <v>143716</v>
+        <v>143723</v>
       </c>
       <c r="G21" s="1">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H21" s="1">
-        <v>35</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="J21" s="21" t="s">
-        <v>61</v>
+        <v>30</v>
+      </c>
+      <c r="I21" s="3">
+        <v>200</v>
+      </c>
+      <c r="J21" s="22" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="1">
-        <v>1018</v>
+      <c r="A22" s="11">
+        <v>2006</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C22" s="1">
         <v>1</v>
@@ -2732,27 +2710,27 @@
         <v>1</v>
       </c>
       <c r="F22" s="3">
-        <v>163681</v>
+        <v>143716</v>
       </c>
       <c r="G22" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H22" s="1">
-        <v>50</v>
-      </c>
-      <c r="I22" s="3">
-        <v>1900</v>
+        <v>35</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="J22" s="21" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="11">
-        <v>1019</v>
+      <c r="A23" s="1">
+        <v>2007</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C23" s="1">
         <v>1</v>
@@ -2764,27 +2742,27 @@
         <v>1</v>
       </c>
       <c r="F23" s="3">
-        <v>143679</v>
+        <v>163681</v>
       </c>
       <c r="G23" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H23" s="1">
         <v>50</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>65</v>
+      <c r="I23" s="3">
+        <v>550</v>
       </c>
       <c r="J23" s="21" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="1">
-        <v>1020</v>
+      <c r="A24" s="11">
+        <v>2008</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C24" s="1">
         <v>1</v>
@@ -2796,24 +2774,27 @@
         <v>1</v>
       </c>
       <c r="F24" s="3">
-        <v>163727</v>
+        <v>143679</v>
       </c>
       <c r="G24" s="1">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H24" s="1">
-        <v>10</v>
-      </c>
-      <c r="J24" s="20" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J24" s="21" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="11">
-        <v>1021</v>
+      <c r="A25" s="1">
+        <v>2009</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C25" s="1">
         <v>1</v>
@@ -2822,30 +2803,27 @@
         <v>2</v>
       </c>
       <c r="E25" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25" s="3">
-        <v>143697</v>
+        <v>163727</v>
       </c>
       <c r="G25" s="1">
-        <v>90</v>
+        <v>8</v>
       </c>
       <c r="H25" s="1">
-        <v>80</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="J25" s="21" t="s">
-        <v>71</v>
+        <v>10</v>
+      </c>
+      <c r="J25" s="20" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="1">
-        <v>1022</v>
+      <c r="A26" s="11">
+        <v>2010</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C26" s="1">
         <v>1</v>
@@ -2857,27 +2835,27 @@
         <v>2</v>
       </c>
       <c r="F26" s="3">
-        <v>146056</v>
+        <v>143697</v>
       </c>
       <c r="G26" s="1">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="H26" s="1">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J26" s="21" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="11">
-        <v>1023</v>
+      <c r="A27" s="1">
+        <v>2011</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C27" s="1">
         <v>1</v>
@@ -2889,70 +2867,60 @@
         <v>2</v>
       </c>
       <c r="F27" s="3">
-        <v>143673</v>
+        <v>146056</v>
       </c>
       <c r="G27" s="1">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="H27" s="1">
         <v>60</v>
       </c>
+      <c r="I27" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="J27" s="21" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="11">
+        <v>2012</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" s="1">
+        <v>1</v>
+      </c>
+      <c r="D28" s="1">
+        <v>2</v>
+      </c>
+      <c r="E28" s="1">
+        <v>2</v>
+      </c>
+      <c r="F28" s="3">
+        <v>143673</v>
+      </c>
+      <c r="G28" s="1">
+        <v>90</v>
+      </c>
+      <c r="H28" s="1">
+        <v>60</v>
+      </c>
+      <c r="J28" s="21" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="1">
-        <v>1024</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="C28" s="1">
-        <v>2</v>
-      </c>
-      <c r="D28" s="1">
-        <v>0</v>
-      </c>
-      <c r="E28" s="1">
-        <v>3</v>
-      </c>
-      <c r="F28" s="3">
-        <v>163636</v>
-      </c>
-      <c r="J28" s="20" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="11">
-        <v>1025</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C29" s="1">
-        <v>2</v>
-      </c>
-      <c r="D29" s="11">
-        <v>0</v>
-      </c>
-      <c r="E29" s="1">
-        <v>3</v>
-      </c>
-      <c r="F29" s="3">
-        <v>143704</v>
-      </c>
-      <c r="J29" s="20" t="s">
-        <v>80</v>
-      </c>
+    <row r="29" spans="2:10">
+      <c r="B29" s="12"/>
+      <c r="J29" s="20"/>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="1">
-        <v>1026</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>81</v>
+        <v>10001</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>77</v>
       </c>
       <c r="C30" s="1">
         <v>2</v>
@@ -2964,18 +2932,18 @@
         <v>3</v>
       </c>
       <c r="F30" s="3">
-        <v>145159</v>
+        <v>163636</v>
       </c>
       <c r="J30" s="20" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="11">
-        <v>1027</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>83</v>
+        <v>10002</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>79</v>
       </c>
       <c r="C31" s="1">
         <v>2</v>
@@ -2987,9 +2955,55 @@
         <v>3</v>
       </c>
       <c r="F31" s="3">
+        <v>143704</v>
+      </c>
+      <c r="J31" s="20" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="1">
+        <v>10003</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" s="1">
+        <v>2</v>
+      </c>
+      <c r="D32" s="1">
+        <v>0</v>
+      </c>
+      <c r="E32" s="1">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3">
+        <v>145159</v>
+      </c>
+      <c r="J32" s="20" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="11">
+        <v>10004</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33" s="1">
+        <v>2</v>
+      </c>
+      <c r="D33" s="11">
+        <v>0</v>
+      </c>
+      <c r="E33" s="1">
+        <v>3</v>
+      </c>
+      <c r="F33" s="3">
         <v>163645</v>
       </c>
-      <c r="J31" s="20" t="s">
+      <c r="J33" s="20" t="s">
         <v>84</v>
       </c>
     </row>

--- a/diurenmw/Excels/SkillObj_技能表.xlsx
+++ b/diurenmw/Excels/SkillObj_技能表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="89">
   <si>
     <t>int</t>
   </si>
@@ -69,6 +69,12 @@
   </si>
   <si>
     <t>describe</t>
+  </si>
+  <si>
+    <t>使用动作资源</t>
+  </si>
+  <si>
+    <t>使用特效资源</t>
   </si>
   <si>
     <t>ID</t>
@@ -816,6 +822,32 @@
         <charset val="134"/>
       </rPr>
       <t>％攻击伤害。</t>
+    </r>
+  </si>
+  <si>
+    <t>活力光环</t>
+  </si>
+  <si>
+    <r>
+      <t>增加角色自身300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的血量恢复速度。</t>
     </r>
   </si>
 </sst>
@@ -1478,6 +1510,7 @@
   </cellStyleXfs>
   <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1486,13 +1519,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1505,7 +1538,6 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -2067,944 +2099,992 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr defaultColWidth="7.46666666666667" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.6814814814815" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.6296296296296" style="2" customWidth="1"/>
-    <col min="3" max="3" width="21.637037037037" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5555555555556" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="21.762962962963" style="3" customWidth="1"/>
-    <col min="7" max="7" width="11.6814814814815" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.1111111111111" style="1" customWidth="1"/>
-    <col min="9" max="9" width="30.9925925925926" style="3" customWidth="1"/>
-    <col min="10" max="10" width="89.5555555555556" style="4" customWidth="1"/>
-    <col min="11" max="16384" width="7.46666666666667" style="5"/>
+    <col min="1" max="2" width="11.3333333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6814814814815" style="2" customWidth="1"/>
+    <col min="4" max="4" width="14.6296296296296" style="3" customWidth="1"/>
+    <col min="5" max="5" width="21.637037037037" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.5555555555556" style="2" customWidth="1"/>
+    <col min="7" max="7" width="16.3333333333333" style="2" customWidth="1"/>
+    <col min="8" max="8" width="21.762962962963" style="4" customWidth="1"/>
+    <col min="9" max="9" width="11.6814814814815" style="2" customWidth="1"/>
+    <col min="10" max="10" width="17.1111111111111" style="2" customWidth="1"/>
+    <col min="11" max="11" width="30.9925925925926" style="4" customWidth="1"/>
+    <col min="12" max="12" width="89.5555555555556" style="5" customWidth="1"/>
+    <col min="13" max="16384" width="7.46666666666667" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1" spans="1:10">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>1</v>
-      </c>
+    <row r="1" ht="18.75" customHeight="1" spans="3:12">
       <c r="C1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>0</v>
+      <c r="D1" s="7" t="s">
+        <v>1</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="7" t="s">
-        <v>1</v>
+      <c r="F1" s="6" t="s">
+        <v>0</v>
       </c>
       <c r="G1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="K1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customHeight="1" spans="1:10">
-      <c r="A2" s="6" t="s">
+      <c r="L1" s="15" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customHeight="1" spans="3:12">
+      <c r="C2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="H2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="I2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="J2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="K2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="L2" s="16" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" ht="44.25" customHeight="1" spans="1:10">
-      <c r="A3" s="6" t="s">
+    <row r="3" ht="44.25" customHeight="1" spans="1:12">
+      <c r="A3" s="8" t="s">
         <v>14</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="11" t="s">
         <v>20</v>
       </c>
       <c r="H3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="I3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="J3" s="10" t="s">
         <v>23</v>
       </c>
+      <c r="K3" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="15" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="4" ht="18.75" customHeight="1"/>
-    <row r="5" spans="1:10">
-      <c r="A5" s="11">
+    <row r="5" spans="3:12">
+      <c r="C5" s="12">
         <v>1001</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="11">
-        <v>1</v>
-      </c>
-      <c r="D5" s="11">
-        <v>1</v>
-      </c>
-      <c r="E5" s="11">
-        <v>1</v>
-      </c>
-      <c r="F5" s="9">
+      <c r="D5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="12">
+        <v>1</v>
+      </c>
+      <c r="F5" s="12">
+        <v>1</v>
+      </c>
+      <c r="G5" s="12">
+        <v>1</v>
+      </c>
+      <c r="H5" s="10">
         <v>98203</v>
       </c>
-      <c r="G5" s="11">
+      <c r="I5" s="12">
         <v>0</v>
       </c>
-      <c r="H5" s="11">
+      <c r="J5" s="12">
         <v>0</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="K5" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" s="18" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" ht="18.75" customHeight="1" spans="3:12">
+      <c r="C6" s="2">
+        <v>1002</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4">
+        <v>312017</v>
+      </c>
+      <c r="I6" s="2">
+        <v>5</v>
+      </c>
+      <c r="J6" s="2">
+        <v>20</v>
+      </c>
+      <c r="K6" s="4">
+        <v>120</v>
+      </c>
+      <c r="L6" s="18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" ht="18.75" customHeight="1" spans="1:12">
+      <c r="A7" s="1">
+        <v>279672</v>
+      </c>
+      <c r="B7" s="1">
+        <v>84958</v>
+      </c>
+      <c r="C7" s="12">
+        <v>1003</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="12">
+        <v>1</v>
+      </c>
+      <c r="F7" s="12">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1</v>
+      </c>
+      <c r="H7" s="4">
+        <v>312027</v>
+      </c>
+      <c r="I7" s="2">
+        <v>5</v>
+      </c>
+      <c r="J7" s="2">
+        <v>20</v>
+      </c>
+      <c r="K7" s="4">
+        <v>140</v>
+      </c>
+      <c r="L7" s="19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" ht="18.75" customHeight="1" spans="3:12">
+      <c r="C8" s="2">
+        <v>1004</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1</v>
+      </c>
+      <c r="H8" s="4">
+        <v>143678</v>
+      </c>
+      <c r="I8" s="2">
+        <v>8</v>
+      </c>
+      <c r="J8" s="2">
+        <v>20</v>
+      </c>
+      <c r="K8" s="4">
+        <v>70</v>
+      </c>
+      <c r="L8" s="19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" ht="18.75" customHeight="1" spans="3:12">
+      <c r="C9" s="12">
+        <v>1005</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2">
+        <v>1</v>
+      </c>
+      <c r="H9" s="4">
+        <v>312012</v>
+      </c>
+      <c r="I9" s="2">
+        <v>10</v>
+      </c>
+      <c r="J9" s="2">
+        <v>30</v>
+      </c>
+      <c r="K9" s="4">
+        <v>330</v>
+      </c>
+      <c r="L9" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" ht="18.75" customHeight="1" spans="3:12">
+      <c r="C10" s="2">
+        <v>1006</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="12">
+        <v>1</v>
+      </c>
+      <c r="F10" s="12">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2">
+        <v>1</v>
+      </c>
+      <c r="H10" s="4">
+        <v>163773</v>
+      </c>
+      <c r="I10" s="2">
+        <v>8</v>
+      </c>
+      <c r="J10" s="2">
         <v>25</v>
       </c>
-      <c r="J5" s="18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" ht="18.75" customHeight="1" spans="1:10">
-      <c r="A6" s="1">
-        <v>1002</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="1">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
-      <c r="F6" s="3">
-        <v>312017</v>
-      </c>
-      <c r="G6" s="1">
+      <c r="K10" s="4">
+        <v>260</v>
+      </c>
+      <c r="L10" s="18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" ht="18.75" customHeight="1" spans="1:12">
+      <c r="A11" s="1">
+        <v>279742</v>
+      </c>
+      <c r="B11" s="1">
+        <v>95654</v>
+      </c>
+      <c r="C11" s="12">
+        <v>1007</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4">
+        <v>312020</v>
+      </c>
+      <c r="I11" s="2">
+        <v>9</v>
+      </c>
+      <c r="J11" s="2">
+        <v>40</v>
+      </c>
+      <c r="K11" s="4">
+        <v>480</v>
+      </c>
+      <c r="L11" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" ht="18.75" customHeight="1" spans="3:12">
+      <c r="C12" s="2">
+        <v>1008</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="12">
+        <v>1</v>
+      </c>
+      <c r="F12" s="12">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2">
+        <v>1</v>
+      </c>
+      <c r="H12" s="4">
+        <v>234347</v>
+      </c>
+      <c r="I12" s="2">
+        <v>12</v>
+      </c>
+      <c r="J12" s="2">
+        <v>50</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="L12" s="19" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="3:12">
+      <c r="C13" s="12">
+        <v>1009</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2">
+        <v>2</v>
+      </c>
+      <c r="H13" s="4">
+        <v>143719</v>
+      </c>
+      <c r="I13" s="2">
+        <v>90</v>
+      </c>
+      <c r="J13" s="2">
+        <v>55</v>
+      </c>
+      <c r="K13" s="4">
+        <v>120</v>
+      </c>
+      <c r="L13" s="20" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="3:12">
+      <c r="C14" s="2">
+        <v>1010</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2">
+        <v>2</v>
+      </c>
+      <c r="H14" s="4">
+        <v>146060</v>
+      </c>
+      <c r="I14" s="2">
+        <v>90</v>
+      </c>
+      <c r="J14" s="2">
+        <v>55</v>
+      </c>
+      <c r="L14" s="20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="1">
+        <v>281700</v>
+      </c>
+      <c r="B15" s="1">
+        <v>297932</v>
+      </c>
+      <c r="C15" s="12">
+        <v>1011</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2">
+        <v>2</v>
+      </c>
+      <c r="H15" s="4">
+        <v>143696</v>
+      </c>
+      <c r="I15" s="2">
+        <v>90</v>
+      </c>
+      <c r="J15" s="2">
+        <v>75</v>
+      </c>
+      <c r="K15" s="4">
+        <v>2600</v>
+      </c>
+      <c r="L15" s="19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="4:12">
+      <c r="D16" s="13"/>
+      <c r="L16" s="21"/>
+    </row>
+    <row r="17" spans="3:12">
+      <c r="C17" s="2">
+        <v>2001</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>2</v>
+      </c>
+      <c r="G17" s="2">
+        <v>1</v>
+      </c>
+      <c r="H17" s="4">
+        <v>163644</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+      <c r="J17" s="2">
+        <v>0</v>
+      </c>
+      <c r="K17" s="4">
+        <v>80</v>
+      </c>
+      <c r="L17" s="21" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="3:12">
+      <c r="C18" s="12">
+        <v>2002</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>2</v>
+      </c>
+      <c r="G18" s="2">
+        <v>1</v>
+      </c>
+      <c r="H18" s="4">
+        <v>163638</v>
+      </c>
+      <c r="I18" s="2">
+        <v>2</v>
+      </c>
+      <c r="J18" s="2">
+        <v>15</v>
+      </c>
+      <c r="K18" s="4">
+        <v>110</v>
+      </c>
+      <c r="L18" s="21" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="3:12">
+      <c r="C19" s="2">
+        <v>2003</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>2</v>
+      </c>
+      <c r="G19" s="2">
+        <v>1</v>
+      </c>
+      <c r="H19" s="4">
+        <v>163680</v>
+      </c>
+      <c r="I19" s="2">
         <v>5</v>
       </c>
-      <c r="H6" s="1">
-        <v>20</v>
-      </c>
-      <c r="I6" s="3">
-        <v>120</v>
-      </c>
-      <c r="J6" s="18" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" ht="18.75" customHeight="1" spans="1:10">
-      <c r="A7" s="11">
-        <v>1003</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="11">
-        <v>1</v>
-      </c>
-      <c r="D7" s="11">
-        <v>1</v>
-      </c>
-      <c r="E7" s="1">
-        <v>1</v>
-      </c>
-      <c r="F7" s="3">
-        <v>312027</v>
-      </c>
-      <c r="G7" s="1">
-        <v>5</v>
-      </c>
-      <c r="H7" s="1">
-        <v>20</v>
-      </c>
-      <c r="I7" s="3">
-        <v>140</v>
-      </c>
-      <c r="J7" s="19" t="s">
+      <c r="J19" s="2">
+        <v>25</v>
+      </c>
+      <c r="K19" s="4">
+        <v>150</v>
+      </c>
+      <c r="L19" s="21" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" spans="3:12">
+      <c r="C20" s="12">
+        <v>2004</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="2">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>2</v>
+      </c>
+      <c r="G20" s="2">
+        <v>1</v>
+      </c>
+      <c r="H20" s="4">
+        <v>163642</v>
+      </c>
+      <c r="I20" s="2">
+        <v>7</v>
+      </c>
+      <c r="J20" s="2">
+        <v>35</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L20" s="21" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="3:12">
+      <c r="C21" s="2">
+        <v>2005</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>2</v>
+      </c>
+      <c r="G21" s="2">
+        <v>1</v>
+      </c>
+      <c r="H21" s="4">
+        <v>143723</v>
+      </c>
+      <c r="I21" s="2">
+        <v>7</v>
+      </c>
+      <c r="J21" s="2">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" ht="18.75" customHeight="1" spans="1:10">
-      <c r="A8" s="1">
-        <v>1004</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="1">
-        <v>1</v>
-      </c>
-      <c r="D8" s="1">
-        <v>1</v>
-      </c>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-      <c r="F8" s="3">
-        <v>143678</v>
-      </c>
-      <c r="G8" s="1">
+      <c r="K21" s="4">
+        <v>200</v>
+      </c>
+      <c r="L21" s="22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12">
+      <c r="C22" s="12">
+        <v>2006</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>2</v>
+      </c>
+      <c r="G22" s="2">
+        <v>1</v>
+      </c>
+      <c r="H22" s="4">
+        <v>143716</v>
+      </c>
+      <c r="I22" s="2">
+        <v>12</v>
+      </c>
+      <c r="J22" s="2">
+        <v>35</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="L22" s="21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12">
+      <c r="C23" s="2">
+        <v>2007</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>2</v>
+      </c>
+      <c r="G23" s="2">
+        <v>1</v>
+      </c>
+      <c r="H23" s="4">
+        <v>163681</v>
+      </c>
+      <c r="I23" s="2">
+        <v>10</v>
+      </c>
+      <c r="J23" s="2">
+        <v>50</v>
+      </c>
+      <c r="K23" s="4">
+        <v>550</v>
+      </c>
+      <c r="L23" s="21" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="3:12">
+      <c r="C24" s="12">
+        <v>2008</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>2</v>
+      </c>
+      <c r="G24" s="2">
+        <v>1</v>
+      </c>
+      <c r="H24" s="4">
+        <v>143679</v>
+      </c>
+      <c r="I24" s="2">
+        <v>15</v>
+      </c>
+      <c r="J24" s="2">
+        <v>50</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="L24" s="21" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" spans="3:12">
+      <c r="C25" s="2">
+        <v>2009</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E25" s="2">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>2</v>
+      </c>
+      <c r="G25" s="2">
+        <v>1</v>
+      </c>
+      <c r="H25" s="4">
+        <v>163727</v>
+      </c>
+      <c r="I25" s="2">
         <v>8</v>
       </c>
-      <c r="H8" s="1">
-        <v>20</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="J25" s="2">
+        <v>10</v>
+      </c>
+      <c r="L25" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J8" s="19" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" ht="18.75" customHeight="1" spans="1:10">
-      <c r="A9" s="11">
-        <v>1005</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="1">
-        <v>1</v>
-      </c>
-      <c r="D9" s="1">
-        <v>1</v>
-      </c>
-      <c r="E9" s="1">
-        <v>1</v>
-      </c>
-      <c r="F9" s="3">
-        <v>312012</v>
-      </c>
-      <c r="G9" s="1">
-        <v>10</v>
-      </c>
-      <c r="H9" s="1">
-        <v>30</v>
-      </c>
-      <c r="I9" s="3">
-        <v>330</v>
-      </c>
-      <c r="J9" s="19" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" ht="18.75" customHeight="1" spans="1:10">
-      <c r="A10" s="1">
-        <v>1006</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="11">
-        <v>1</v>
-      </c>
-      <c r="D10" s="11">
-        <v>1</v>
-      </c>
-      <c r="E10" s="1">
-        <v>1</v>
-      </c>
-      <c r="F10" s="3">
-        <v>163773</v>
-      </c>
-      <c r="G10" s="1">
-        <v>8</v>
-      </c>
-      <c r="H10" s="1">
-        <v>25</v>
-      </c>
-      <c r="I10" s="3">
-        <v>260</v>
-      </c>
-      <c r="J10" s="18" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" ht="18.75" customHeight="1" spans="1:10">
-      <c r="A11" s="11">
-        <v>1007</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="1">
-        <v>1</v>
-      </c>
-      <c r="D11" s="1">
-        <v>1</v>
-      </c>
-      <c r="E11" s="1">
-        <v>1</v>
-      </c>
-      <c r="F11" s="3">
-        <v>312020</v>
-      </c>
-      <c r="G11" s="1">
-        <v>9</v>
-      </c>
-      <c r="H11" s="1">
-        <v>40</v>
-      </c>
-      <c r="I11" s="3">
-        <v>480</v>
-      </c>
-      <c r="J11" s="18" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" ht="18.75" customHeight="1" spans="1:10">
-      <c r="A12" s="1">
-        <v>1008</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="11">
-        <v>1</v>
-      </c>
-      <c r="D12" s="11">
-        <v>1</v>
-      </c>
-      <c r="E12" s="1">
-        <v>1</v>
-      </c>
-      <c r="F12" s="3">
-        <v>234347</v>
-      </c>
-      <c r="G12" s="1">
-        <v>12</v>
-      </c>
-      <c r="H12" s="1">
-        <v>50</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J12" s="19" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="11">
-        <v>1009</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="1">
-        <v>1</v>
-      </c>
-      <c r="D13" s="1">
-        <v>1</v>
-      </c>
-      <c r="E13" s="1">
+    </row>
+    <row r="26" spans="3:12">
+      <c r="C26" s="12">
+        <v>2010</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E26" s="2">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
         <v>2</v>
       </c>
-      <c r="F13" s="3">
-        <v>143719</v>
-      </c>
-      <c r="G13" s="1">
+      <c r="G26" s="2">
+        <v>2</v>
+      </c>
+      <c r="H26" s="4">
+        <v>143697</v>
+      </c>
+      <c r="I26" s="2">
         <v>90</v>
       </c>
-      <c r="H13" s="1">
-        <v>55</v>
-      </c>
-      <c r="I13" s="3">
-        <v>120</v>
-      </c>
-      <c r="J13" s="20" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="1">
-        <v>1010</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="1">
-        <v>1</v>
-      </c>
-      <c r="D14" s="1">
-        <v>1</v>
-      </c>
-      <c r="E14" s="1">
+      <c r="J26" s="2">
+        <v>80</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L26" s="21" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27" spans="3:12">
+      <c r="C27" s="2">
+        <v>2011</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
         <v>2</v>
       </c>
-      <c r="F14" s="3">
-        <v>146060</v>
-      </c>
-      <c r="G14" s="1">
+      <c r="G27" s="2">
+        <v>2</v>
+      </c>
+      <c r="H27" s="4">
+        <v>146056</v>
+      </c>
+      <c r="I27" s="2">
+        <v>75</v>
+      </c>
+      <c r="J27" s="2">
+        <v>60</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="L27" s="21" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28" spans="3:12">
+      <c r="C28" s="12">
+        <v>2012</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="E28" s="2">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>2</v>
+      </c>
+      <c r="G28" s="2">
+        <v>2</v>
+      </c>
+      <c r="H28" s="4">
+        <v>143673</v>
+      </c>
+      <c r="I28" s="2">
         <v>90</v>
       </c>
-      <c r="H14" s="1">
-        <v>55</v>
-      </c>
-      <c r="J14" s="20" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="11">
-        <v>1011</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="1">
-        <v>1</v>
-      </c>
-      <c r="D15" s="1">
-        <v>1</v>
-      </c>
-      <c r="E15" s="1">
+      <c r="J28" s="2">
+        <v>60</v>
+      </c>
+      <c r="L28" s="21" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" spans="4:12">
+      <c r="D29" s="8"/>
+      <c r="L29" s="20"/>
+    </row>
+    <row r="30" spans="3:12">
+      <c r="C30" s="2">
+        <v>10001</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E30" s="2">
         <v>2</v>
       </c>
-      <c r="F15" s="3">
-        <v>143696</v>
-      </c>
-      <c r="G15" s="1">
-        <v>90</v>
-      </c>
-      <c r="H15" s="1">
-        <v>75</v>
-      </c>
-      <c r="I15" s="3">
-        <v>2600</v>
-      </c>
-      <c r="J15" s="19" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10">
-      <c r="B16" s="13"/>
-      <c r="J16" s="21"/>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="1">
-        <v>2001</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="1">
-        <v>1</v>
-      </c>
-      <c r="D17" s="1">
+      <c r="F30" s="2">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2">
+        <v>3</v>
+      </c>
+      <c r="H30" s="4">
+        <v>163636</v>
+      </c>
+      <c r="L30" s="20" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12">
+      <c r="C31" s="12">
+        <v>10002</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="E31" s="2">
         <v>2</v>
       </c>
-      <c r="E17" s="1">
-        <v>1</v>
-      </c>
-      <c r="F17" s="3">
-        <v>163644</v>
-      </c>
-      <c r="G17" s="1">
+      <c r="F31" s="12">
         <v>0</v>
       </c>
-      <c r="H17" s="1">
+      <c r="G31" s="2">
+        <v>3</v>
+      </c>
+      <c r="H31" s="4">
+        <v>143704</v>
+      </c>
+      <c r="L31" s="20" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12">
+      <c r="C32" s="2">
+        <v>10003</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="E32" s="2">
+        <v>2</v>
+      </c>
+      <c r="F32" s="2">
         <v>0</v>
       </c>
-      <c r="I17" s="3">
-        <v>80</v>
-      </c>
-      <c r="J17" s="21" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="11">
-        <v>2002</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="1">
-        <v>1</v>
-      </c>
-      <c r="D18" s="1">
+      <c r="G32" s="2">
+        <v>3</v>
+      </c>
+      <c r="H32" s="4">
+        <v>145159</v>
+      </c>
+      <c r="L32" s="20" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" spans="3:12">
+      <c r="C33" s="12">
+        <v>10004</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="E33" s="2">
         <v>2</v>
       </c>
-      <c r="E18" s="1">
-        <v>1</v>
-      </c>
-      <c r="F18" s="3">
-        <v>163638</v>
-      </c>
-      <c r="G18" s="1">
+      <c r="F33" s="12">
+        <v>0</v>
+      </c>
+      <c r="G33" s="2">
+        <v>3</v>
+      </c>
+      <c r="H33" s="4">
+        <v>163645</v>
+      </c>
+      <c r="L33" s="20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" spans="3:12">
+      <c r="C34" s="2">
+        <v>10004</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="E34" s="2">
         <v>2</v>
       </c>
-      <c r="H18" s="1">
-        <v>15</v>
-      </c>
-      <c r="I18" s="3">
-        <v>110</v>
-      </c>
-      <c r="J18" s="21" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="1">
-        <v>2003</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" s="1">
-        <v>1</v>
-      </c>
-      <c r="D19" s="1">
-        <v>2</v>
-      </c>
-      <c r="E19" s="1">
-        <v>1</v>
-      </c>
-      <c r="F19" s="3">
-        <v>163680</v>
-      </c>
-      <c r="G19" s="1">
-        <v>5</v>
-      </c>
-      <c r="H19" s="1">
-        <v>25</v>
-      </c>
-      <c r="I19" s="3">
-        <v>150</v>
-      </c>
-      <c r="J19" s="21" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="11">
-        <v>2004</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="C20" s="1">
-        <v>1</v>
-      </c>
-      <c r="D20" s="1">
-        <v>2</v>
-      </c>
-      <c r="E20" s="1">
-        <v>1</v>
-      </c>
-      <c r="F20" s="3">
-        <v>163642</v>
-      </c>
-      <c r="G20" s="1">
-        <v>7</v>
-      </c>
-      <c r="H20" s="1">
-        <v>35</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="J20" s="21" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="1">
-        <v>2005</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" s="1">
-        <v>1</v>
-      </c>
-      <c r="D21" s="1">
-        <v>2</v>
-      </c>
-      <c r="E21" s="1">
-        <v>1</v>
-      </c>
-      <c r="F21" s="3">
-        <v>143723</v>
-      </c>
-      <c r="G21" s="1">
-        <v>7</v>
-      </c>
-      <c r="H21" s="1">
-        <v>30</v>
-      </c>
-      <c r="I21" s="3">
-        <v>200</v>
-      </c>
-      <c r="J21" s="22" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="11">
-        <v>2006</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22" s="1">
-        <v>1</v>
-      </c>
-      <c r="D22" s="1">
-        <v>2</v>
-      </c>
-      <c r="E22" s="1">
-        <v>1</v>
-      </c>
-      <c r="F22" s="3">
-        <v>143716</v>
-      </c>
-      <c r="G22" s="1">
-        <v>12</v>
-      </c>
-      <c r="H22" s="1">
-        <v>35</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="J22" s="21" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="1">
-        <v>2007</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C23" s="1">
-        <v>1</v>
-      </c>
-      <c r="D23" s="1">
-        <v>2</v>
-      </c>
-      <c r="E23" s="1">
-        <v>1</v>
-      </c>
-      <c r="F23" s="3">
-        <v>163681</v>
-      </c>
-      <c r="G23" s="1">
-        <v>10</v>
-      </c>
-      <c r="H23" s="1">
-        <v>50</v>
-      </c>
-      <c r="I23" s="3">
-        <v>550</v>
-      </c>
-      <c r="J23" s="21" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="11">
-        <v>2008</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="1">
-        <v>1</v>
-      </c>
-      <c r="D24" s="1">
-        <v>2</v>
-      </c>
-      <c r="E24" s="1">
-        <v>1</v>
-      </c>
-      <c r="F24" s="3">
-        <v>143679</v>
-      </c>
-      <c r="G24" s="1">
-        <v>15</v>
-      </c>
-      <c r="H24" s="1">
-        <v>50</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J24" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="1">
-        <v>2009</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="C25" s="1">
-        <v>1</v>
-      </c>
-      <c r="D25" s="1">
-        <v>2</v>
-      </c>
-      <c r="E25" s="1">
-        <v>1</v>
-      </c>
-      <c r="F25" s="3">
-        <v>163727</v>
-      </c>
-      <c r="G25" s="1">
-        <v>8</v>
-      </c>
-      <c r="H25" s="1">
-        <v>10</v>
-      </c>
-      <c r="J25" s="20" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="11">
-        <v>2010</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C26" s="1">
-        <v>1</v>
-      </c>
-      <c r="D26" s="1">
-        <v>2</v>
-      </c>
-      <c r="E26" s="1">
-        <v>2</v>
-      </c>
-      <c r="F26" s="3">
-        <v>143697</v>
-      </c>
-      <c r="G26" s="1">
-        <v>90</v>
-      </c>
-      <c r="H26" s="1">
-        <v>80</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="J26" s="21" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="1">
-        <v>2011</v>
-      </c>
-      <c r="B27" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C27" s="1">
-        <v>1</v>
-      </c>
-      <c r="D27" s="1">
-        <v>2</v>
-      </c>
-      <c r="E27" s="1">
-        <v>2</v>
-      </c>
-      <c r="F27" s="3">
-        <v>146056</v>
-      </c>
-      <c r="G27" s="1">
-        <v>75</v>
-      </c>
-      <c r="H27" s="1">
-        <v>60</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="J27" s="21" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="11">
-        <v>2012</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C28" s="1">
-        <v>1</v>
-      </c>
-      <c r="D28" s="1">
-        <v>2</v>
-      </c>
-      <c r="E28" s="1">
-        <v>2</v>
-      </c>
-      <c r="F28" s="3">
-        <v>143673</v>
-      </c>
-      <c r="G28" s="1">
-        <v>90</v>
-      </c>
-      <c r="H28" s="1">
-        <v>60</v>
-      </c>
-      <c r="J28" s="21" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10">
-      <c r="B29" s="12"/>
-      <c r="J29" s="20"/>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="1">
-        <v>10001</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="C30" s="1">
-        <v>2</v>
-      </c>
-      <c r="D30" s="1">
+      <c r="F34" s="2">
         <v>0</v>
       </c>
-      <c r="E30" s="1">
+      <c r="G34" s="2">
         <v>3</v>
       </c>
-      <c r="F30" s="3">
-        <v>163636</v>
-      </c>
-      <c r="J30" s="20" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="11">
-        <v>10002</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C31" s="1">
-        <v>2</v>
-      </c>
-      <c r="D31" s="11">
-        <v>0</v>
-      </c>
-      <c r="E31" s="1">
-        <v>3</v>
-      </c>
-      <c r="F31" s="3">
-        <v>143704</v>
-      </c>
-      <c r="J31" s="20" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
-      <c r="A32" s="1">
-        <v>10003</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="C32" s="1">
-        <v>2</v>
-      </c>
-      <c r="D32" s="1">
-        <v>0</v>
-      </c>
-      <c r="E32" s="1">
-        <v>3</v>
-      </c>
-      <c r="F32" s="3">
-        <v>145159</v>
-      </c>
-      <c r="J32" s="20" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
-      <c r="A33" s="11">
-        <v>10004</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C33" s="1">
-        <v>2</v>
-      </c>
-      <c r="D33" s="11">
-        <v>0</v>
-      </c>
-      <c r="E33" s="1">
-        <v>3</v>
-      </c>
-      <c r="F33" s="3">
-        <v>163645</v>
-      </c>
-      <c r="J33" s="20" t="s">
-        <v>84</v>
+      <c r="H34" s="4">
+        <v>143703</v>
+      </c>
+      <c r="L34" s="20" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/diurenmw/Excels/SkillObj_技能表.xlsx
+++ b/diurenmw/Excels/SkillObj_技能表.xlsx
@@ -1609,13 +1609,13 @@
         <v>143696</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="H17" s="1" t="n">
         <v>75</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>2600</v>
+        <v>260</v>
       </c>
       <c r="J17" s="16" t="s">
         <v>48</v>

--- a/diurenmw/Excels/SkillObj_技能表.xlsx
+++ b/diurenmw/Excels/SkillObj_技能表.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="90">
   <si>
     <t xml:space="preserve">int</t>
   </si>
@@ -540,6 +540,9 @@
   </si>
   <si>
     <t xml:space="preserve">天地一刀斩</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1000|260|260|260</t>
   </si>
   <si>
     <t xml:space="preserve">携万钧之势一刀斩下，对前方超大范围造成一次超高伤害。</t>
@@ -1614,11 +1617,11 @@
       <c r="H17" s="1" t="n">
         <v>75</v>
       </c>
-      <c r="I17" s="3" t="n">
-        <v>260</v>
+      <c r="I17" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="J17" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>281700</v>
@@ -1632,7 +1635,7 @@
         <v>1014</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>1</v>
@@ -1663,7 +1666,7 @@
         <v>2001</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>1</v>
@@ -1687,7 +1690,7 @@
         <v>80</v>
       </c>
       <c r="J20" s="20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1695,7 +1698,7 @@
         <v>2002</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>1</v>
@@ -1719,7 +1722,7 @@
         <v>110</v>
       </c>
       <c r="J21" s="20" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1727,7 +1730,7 @@
         <v>2003</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>1</v>
@@ -1751,7 +1754,7 @@
         <v>150</v>
       </c>
       <c r="J22" s="20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1759,7 +1762,7 @@
         <v>2004</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>1</v>
@@ -1780,10 +1783,10 @@
         <v>35</v>
       </c>
       <c r="I23" s="18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J23" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1791,7 +1794,7 @@
         <v>2005</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>1</v>
@@ -1815,7 +1818,7 @@
         <v>200</v>
       </c>
       <c r="J24" s="20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1823,7 +1826,7 @@
         <v>2006</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>1</v>
@@ -1844,10 +1847,10 @@
         <v>35</v>
       </c>
       <c r="I25" s="18" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J25" s="20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1855,7 +1858,7 @@
         <v>2007</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>1</v>
@@ -1879,7 +1882,7 @@
         <v>550</v>
       </c>
       <c r="J26" s="20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1887,7 +1890,7 @@
         <v>2008</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>1</v>
@@ -1908,10 +1911,10 @@
         <v>50</v>
       </c>
       <c r="I27" s="18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J27" s="20" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1919,7 +1922,7 @@
         <v>2009</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>1</v>
@@ -1940,7 +1943,7 @@
         <v>10</v>
       </c>
       <c r="J28" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1948,7 +1951,7 @@
         <v>2010</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>1</v>
@@ -1969,10 +1972,10 @@
         <v>80</v>
       </c>
       <c r="I29" s="18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J29" s="20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1980,7 +1983,7 @@
         <v>2011</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>1</v>
@@ -2001,10 +2004,10 @@
         <v>60</v>
       </c>
       <c r="I30" s="18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J30" s="20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2012,7 +2015,7 @@
         <v>2012</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>1</v>
@@ -2033,7 +2036,7 @@
         <v>60</v>
       </c>
       <c r="J31" s="20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2045,7 +2048,7 @@
         <v>10001</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>2</v>
@@ -2060,7 +2063,7 @@
         <v>163636</v>
       </c>
       <c r="J33" s="13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2068,7 +2071,7 @@
         <v>10002</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>2</v>
@@ -2083,7 +2086,7 @@
         <v>143704</v>
       </c>
       <c r="J34" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2091,7 +2094,7 @@
         <v>10003</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>2</v>
@@ -2106,7 +2109,7 @@
         <v>145159</v>
       </c>
       <c r="J35" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2114,7 +2117,7 @@
         <v>10004</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>2</v>
@@ -2129,7 +2132,7 @@
         <v>163645</v>
       </c>
       <c r="J36" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2137,7 +2140,7 @@
         <v>10005</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>2</v>
@@ -2152,7 +2155,7 @@
         <v>143703</v>
       </c>
       <c r="J37" s="13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/diurenmw/Excels/SkillObj_技能表.xlsx
+++ b/diurenmw/Excels/SkillObj_技能表.xlsx
@@ -364,7 +364,7 @@
     <t xml:space="preserve">将自身的气力附着于武器之上并向前挥出，对处于一条直线的敌人造成伤害。</t>
   </si>
   <si>
-    <t xml:space="preserve">六合锁</t>
+    <t xml:space="preserve">血爆</t>
   </si>
   <si>
     <t xml:space="preserve">向周围抛出多道锁链，将周围的敌人抓取到身边（对BOSS无效），并击碎敌人防御力10％。</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">天地一刀斩</t>
   </si>
   <si>
-    <t xml:space="preserve">1000|260|260|260</t>
+    <t xml:space="preserve">3000|1260|1260|1260</t>
   </si>
   <si>
     <t xml:space="preserve">携万钧之势一刀斩下，对前方超大范围造成一次超高伤害。</t>
@@ -1382,13 +1382,13 @@
         <v>143678</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H10" s="1" t="n">
         <v>20</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>70</v>
+        <v>3000</v>
       </c>
       <c r="J10" s="16" t="s">
         <v>33</v>
@@ -1446,7 +1446,7 @@
         <v>163773</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H12" s="1" t="n">
         <v>25</v>

--- a/diurenmw/Excels/SkillObj_技能表.xlsx
+++ b/diurenmw/Excels/SkillObj_技能表.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="91">
   <si>
     <t xml:space="preserve">int</t>
   </si>
@@ -370,7 +370,10 @@
     <t xml:space="preserve">向周围抛出多道锁链，将周围的敌人抓取到身边（对BOSS无效），并击碎敌人防御力10％。</t>
   </si>
   <si>
-    <t xml:space="preserve">冲锋</t>
+    <t xml:space="preserve">怒气爆发</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330|100</t>
   </si>
   <si>
     <r>
@@ -1419,11 +1422,11 @@
       <c r="H11" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="I11" s="3" t="n">
-        <v>330</v>
+      <c r="I11" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="J11" s="16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1431,7 +1434,7 @@
         <v>1008</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C12" s="15" t="n">
         <v>1</v>
@@ -1455,7 +1458,7 @@
         <v>260</v>
       </c>
       <c r="J12" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>269092</v>
@@ -1466,7 +1469,7 @@
         <v>1009</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>1</v>
@@ -1490,7 +1493,7 @@
         <v>480</v>
       </c>
       <c r="J13" s="16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>279742</v>
@@ -1504,7 +1507,7 @@
         <v>1010</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C14" s="15" t="n">
         <v>1</v>
@@ -1525,10 +1528,10 @@
         <v>50</v>
       </c>
       <c r="I14" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J14" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1536,7 +1539,7 @@
         <v>1011</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>1</v>
@@ -1560,7 +1563,7 @@
         <v>120</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1568,7 +1571,7 @@
         <v>1012</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>1</v>
@@ -1589,7 +1592,7 @@
         <v>55</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1597,7 +1600,7 @@
         <v>1013</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>1</v>
@@ -1618,10 +1621,10 @@
         <v>75</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J17" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>281700</v>
@@ -1635,7 +1638,7 @@
         <v>1014</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>1</v>
@@ -1666,7 +1669,7 @@
         <v>2001</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>1</v>
@@ -1690,7 +1693,7 @@
         <v>80</v>
       </c>
       <c r="J20" s="20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1698,7 +1701,7 @@
         <v>2002</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>1</v>
@@ -1722,7 +1725,7 @@
         <v>110</v>
       </c>
       <c r="J21" s="20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1730,7 +1733,7 @@
         <v>2003</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>1</v>
@@ -1754,7 +1757,7 @@
         <v>150</v>
       </c>
       <c r="J22" s="20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1762,7 +1765,7 @@
         <v>2004</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>1</v>
@@ -1783,10 +1786,10 @@
         <v>35</v>
       </c>
       <c r="I23" s="18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J23" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1794,7 +1797,7 @@
         <v>2005</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>1</v>
@@ -1818,7 +1821,7 @@
         <v>200</v>
       </c>
       <c r="J24" s="20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1826,7 +1829,7 @@
         <v>2006</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>1</v>
@@ -1847,10 +1850,10 @@
         <v>35</v>
       </c>
       <c r="I25" s="18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J25" s="20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1858,7 +1861,7 @@
         <v>2007</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>1</v>
@@ -1882,7 +1885,7 @@
         <v>550</v>
       </c>
       <c r="J26" s="20" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1890,7 +1893,7 @@
         <v>2008</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>1</v>
@@ -1911,10 +1914,10 @@
         <v>50</v>
       </c>
       <c r="I27" s="18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J27" s="20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1922,7 +1925,7 @@
         <v>2009</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>1</v>
@@ -1943,7 +1946,7 @@
         <v>10</v>
       </c>
       <c r="J28" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1951,7 +1954,7 @@
         <v>2010</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>1</v>
@@ -1972,10 +1975,10 @@
         <v>80</v>
       </c>
       <c r="I29" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J29" s="20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1983,7 +1986,7 @@
         <v>2011</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>1</v>
@@ -2004,10 +2007,10 @@
         <v>60</v>
       </c>
       <c r="I30" s="18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J30" s="20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2015,7 +2018,7 @@
         <v>2012</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>1</v>
@@ -2036,7 +2039,7 @@
         <v>60</v>
       </c>
       <c r="J31" s="20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2048,7 +2051,7 @@
         <v>10001</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>2</v>
@@ -2063,7 +2066,7 @@
         <v>163636</v>
       </c>
       <c r="J33" s="13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2071,7 +2074,7 @@
         <v>10002</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>2</v>
@@ -2086,7 +2089,7 @@
         <v>143704</v>
       </c>
       <c r="J34" s="13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2094,7 +2097,7 @@
         <v>10003</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>2</v>
@@ -2109,7 +2112,7 @@
         <v>145159</v>
       </c>
       <c r="J35" s="13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2117,7 +2120,7 @@
         <v>10004</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>2</v>
@@ -2132,7 +2135,7 @@
         <v>163645</v>
       </c>
       <c r="J36" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2140,7 +2143,7 @@
         <v>10005</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>2</v>
@@ -2155,7 +2158,7 @@
         <v>143703</v>
       </c>
       <c r="J37" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/diurenmw/Excels/SkillObj_技能表.xlsx
+++ b/diurenmw/Excels/SkillObj_技能表.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="103">
   <si>
     <t xml:space="preserve">int</t>
   </si>
@@ -545,42 +545,25 @@
     <t xml:space="preserve">16000|5000|5000|5000</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">召唤出血气之剑并猛力捶击地面， 使地面出现大范围的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">炙热岩浆</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">攻击敌人并使其浮空。</t>
-    </r>
+    <t xml:space="preserve">召唤出血气之剑并猛力捶击地面， 使地面出现大范围的炙热岩浆攻击敌人并使其浮空。</t>
   </si>
   <si>
     <t xml:space="preserve">锤击伤害：16000%物理攻击力||岩浆攻击力：5000%物理攻击力</t>
   </si>
   <si>
     <t xml:space="preserve">后跳</t>
+  </si>
+  <si>
+    <t xml:space="preserve">普通攻击1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">发射火球</t>
+  </si>
+  <si>
+    <t xml:space="preserve">无</t>
+  </si>
+  <si>
+    <t xml:space="preserve">普通攻击2</t>
   </si>
   <si>
     <t xml:space="preserve">冰锥术</t>
@@ -938,18 +921,18 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1004,7 +987,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1051,15 +1034,15 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1080,21 +1063,21 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
-  <sheetFormatPr defaultColWidth="7.46875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:M41"/>
+  <sheetFormatPr defaultColWidth="7.46875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="12.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="25.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="18.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="4" width="21.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="4" width="14.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="4" width="26.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="77.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="37.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="4" width="9.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="10.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="21.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="16.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="4" width="18.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="4" width="12.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="4" width="22.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="66.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="32.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="4" width="8.36"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1167,7 +1150,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="81" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
         <v>15</v>
       </c>
@@ -1492,7 +1475,7 @@
       <c r="J12" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="K12" s="14" t="s">
+      <c r="K12" s="11" t="s">
         <v>45</v>
       </c>
       <c r="L12" s="13" t="n">
@@ -1629,7 +1612,7 @@
       <c r="H16" s="13" t="n">
         <v>55</v>
       </c>
-      <c r="I16" s="4" t="n">
+      <c r="I16" s="13" t="n">
         <v>100</v>
       </c>
       <c r="J16" s="11" t="s">
@@ -1697,7 +1680,7 @@
       <c r="F18" s="10" t="n">
         <v>37792</v>
       </c>
-      <c r="G18" s="15" t="n">
+      <c r="G18" s="14" t="n">
         <v>0.5</v>
       </c>
       <c r="H18" s="13" t="n">
@@ -1706,508 +1689,507 @@
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
     </row>
-    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="11"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-    </row>
-    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="n">
+    <row r="19" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="n">
         <v>2001</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B21" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="C20" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="10" t="n">
+      <c r="C21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>98203</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J21" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="K21" s="15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="16" t="n">
+        <v>98203</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J22" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="K22" s="15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="16" t="n">
+        <v>37792</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+    </row>
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="10" t="n">
         <v>163644</v>
       </c>
-      <c r="G20" s="13" t="n">
+      <c r="G24" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="13" t="n">
+      <c r="H24" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="10" t="n">
+      <c r="I24" s="10" t="n">
         <v>80</v>
       </c>
-      <c r="J20" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="K20" s="16"/>
-    </row>
-    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="n">
-        <v>2002</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="10" t="n">
+      <c r="J24" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="K24" s="15"/>
+    </row>
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="10" t="n">
         <v>163638</v>
       </c>
-      <c r="G21" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="H21" s="13" t="n">
+      <c r="G25" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="I21" s="10" t="n">
+      <c r="I25" s="10" t="n">
         <v>110</v>
       </c>
-      <c r="J21" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="K21" s="16"/>
-    </row>
-    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13" t="n">
-        <v>2003</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E22" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="10" t="n">
+      <c r="J25" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="K25" s="15"/>
+    </row>
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="10" t="n">
         <v>163680</v>
       </c>
-      <c r="G22" s="13" t="n">
+      <c r="G26" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="H22" s="13" t="n">
+      <c r="H26" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="I22" s="10" t="n">
+      <c r="I26" s="10" t="n">
         <v>150</v>
       </c>
-      <c r="J22" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="K22" s="16"/>
-    </row>
-    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="n">
-        <v>2004</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="C23" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E23" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="10" t="n">
+      <c r="J26" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="K26" s="15"/>
+    </row>
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="10" t="n">
         <v>163642</v>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="G27" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="H23" s="13" t="n">
+      <c r="H27" s="13" t="n">
         <v>35</v>
       </c>
-      <c r="I23" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="J23" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="K23" s="16"/>
-    </row>
-    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="n">
-        <v>2005</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C24" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E24" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="10" t="n">
+      <c r="I27" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="J27" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="K27" s="15"/>
+    </row>
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="10" t="n">
         <v>143723</v>
       </c>
-      <c r="G24" s="13" t="n">
+      <c r="G28" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="H24" s="13" t="n">
+      <c r="H28" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="I24" s="10" t="n">
+      <c r="I28" s="10" t="n">
         <v>200</v>
       </c>
-      <c r="J24" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="K24" s="16"/>
-    </row>
-    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13" t="n">
-        <v>2006</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C25" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="10" t="n">
+      <c r="J28" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="K28" s="15"/>
+    </row>
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="10" t="n">
         <v>143716</v>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="G29" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="H25" s="13" t="n">
+      <c r="H29" s="13" t="n">
         <v>35</v>
       </c>
-      <c r="I25" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="J25" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="K25" s="16"/>
-    </row>
-    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="13" t="n">
-        <v>2007</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C26" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E26" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="10" t="n">
+      <c r="I29" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="J29" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="K29" s="15"/>
+    </row>
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C30" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="10" t="n">
         <v>163681</v>
       </c>
-      <c r="G26" s="13" t="n">
+      <c r="G30" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="H26" s="13" t="n">
+      <c r="H30" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="I26" s="10" t="n">
+      <c r="I30" s="10" t="n">
         <v>550</v>
       </c>
-      <c r="J26" s="16" t="s">
+      <c r="J30" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="K30" s="15"/>
+    </row>
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C31" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>143679</v>
+      </c>
+      <c r="G31" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="H31" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="J31" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="K31" s="15"/>
+    </row>
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>163727</v>
+      </c>
+      <c r="G32" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="H32" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="J32" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="K32" s="11"/>
+    </row>
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" s="10" t="n">
+        <v>143697</v>
+      </c>
+      <c r="G33" s="13" t="n">
+        <v>90</v>
+      </c>
+      <c r="H33" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="J33" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="K33" s="15"/>
+    </row>
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>146056</v>
+      </c>
+      <c r="G34" s="13" t="n">
         <v>75</v>
       </c>
-      <c r="K26" s="16"/>
-    </row>
-    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13" t="n">
-        <v>2008</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C27" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E27" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="10" t="n">
-        <v>143679</v>
-      </c>
-      <c r="G27" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="H27" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="J27" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="K27" s="16"/>
-    </row>
-    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13" t="n">
-        <v>2009</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C28" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E28" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="10" t="n">
-        <v>163727</v>
-      </c>
-      <c r="G28" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="H28" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="J28" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="K28" s="11"/>
-    </row>
-    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13" t="n">
-        <v>2010</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="C29" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E29" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F29" s="10" t="n">
-        <v>143697</v>
-      </c>
-      <c r="G29" s="13" t="n">
+      <c r="H34" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="J34" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="H29" s="13" t="n">
-        <v>80</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="J29" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="K29" s="16"/>
-    </row>
-    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13" t="n">
-        <v>2011</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="C30" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E30" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F30" s="10" t="n">
-        <v>146056</v>
-      </c>
-      <c r="G30" s="13" t="n">
-        <v>75</v>
-      </c>
-      <c r="H30" s="13" t="n">
+      <c r="K34" s="15"/>
+    </row>
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C35" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" s="10" t="n">
+        <v>143673</v>
+      </c>
+      <c r="G35" s="13" t="n">
+        <v>90</v>
+      </c>
+      <c r="H35" s="13" t="n">
         <v>60</v>
       </c>
-      <c r="I30" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="J30" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="K30" s="16"/>
-    </row>
-    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13" t="n">
-        <v>2012</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="C31" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E31" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F31" s="10" t="n">
-        <v>143673</v>
-      </c>
-      <c r="G31" s="13" t="n">
-        <v>90</v>
-      </c>
-      <c r="H31" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="J31" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="K31" s="16"/>
-    </row>
-    <row r="32" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="11"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11"/>
-    </row>
-    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="13" t="n">
+      <c r="J35" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="K35" s="15"/>
+    </row>
+    <row r="36" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="11"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+    </row>
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="13" t="n">
         <v>10001</v>
       </c>
-      <c r="B33" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="C33" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="F33" s="10" t="n">
-        <v>163636</v>
-      </c>
-      <c r="J33" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="K33" s="11"/>
-    </row>
-    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="13" t="n">
-        <v>10002</v>
-      </c>
-      <c r="B34" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="C34" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D34" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="F34" s="10" t="n">
-        <v>143704</v>
-      </c>
-      <c r="J34" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="K34" s="11"/>
-    </row>
-    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="13" t="n">
-        <v>10003</v>
-      </c>
-      <c r="B35" s="11" t="s">
+      <c r="B37" s="11" t="s">
         <v>93</v>
-      </c>
-      <c r="C35" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D35" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="F35" s="10" t="n">
-        <v>145159</v>
-      </c>
-      <c r="J35" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="K35" s="11"/>
-    </row>
-    <row r="36" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="13" t="n">
-        <v>10004</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C36" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D36" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="F36" s="10" t="n">
-        <v>163645</v>
-      </c>
-      <c r="J36" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="K36" s="11"/>
-    </row>
-    <row r="37" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="13" t="n">
-        <v>10005</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>97</v>
       </c>
       <c r="C37" s="13" t="n">
         <v>2</v>
@@ -2219,12 +2201,108 @@
         <v>3</v>
       </c>
       <c r="F37" s="10" t="n">
+        <v>163636</v>
+      </c>
+      <c r="J37" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="K37" s="11"/>
+    </row>
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="13" t="n">
+        <v>10002</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C38" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>143704</v>
+      </c>
+      <c r="J38" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="K38" s="11"/>
+    </row>
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="13" t="n">
+        <v>10003</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="C39" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" s="10" t="n">
+        <v>145159</v>
+      </c>
+      <c r="J39" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="K39" s="11"/>
+    </row>
+    <row r="40" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="13" t="n">
+        <v>10004</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C40" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>163645</v>
+      </c>
+      <c r="J40" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="K40" s="11"/>
+    </row>
+    <row r="41" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="13" t="n">
+        <v>10005</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C41" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" s="10" t="n">
         <v>143703</v>
       </c>
-      <c r="J37" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="K37" s="11"/>
+      <c r="J41" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="K41" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/diurenmw/Excels/SkillObj_技能表.xlsx
+++ b/diurenmw/Excels/SkillObj_技能表.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="103">
   <si>
     <t xml:space="preserve">int</t>
   </si>
@@ -599,7 +599,7 @@
     <t xml:space="preserve">向敌人发射一道最多弹射6次的闪电链，优先弹射新敌人，僵直敌人并造成伤害。对同一敌人伤害递减20％。</t>
   </si>
   <si>
-    <t xml:space="preserve">万雷引</t>
+    <t xml:space="preserve">湮灭黑洞</t>
   </si>
   <si>
     <t xml:space="preserve">75|75|75|75|75</t>
@@ -1077,7 +1077,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="4" width="22.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="66.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="32.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="4" width="8.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="4" width="8.35"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1974,7 +1974,7 @@
         <v>143716</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H29" s="13" t="n">
         <v>35</v>
@@ -1985,7 +1985,9 @@
       <c r="J29" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="K29" s="15"/>
+      <c r="K29" s="15" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="n">

--- a/diurenmw/Excels/SkillObj_技能表.xlsx
+++ b/diurenmw/Excels/SkillObj_技能表.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="103">
   <si>
     <t xml:space="preserve">int</t>
   </si>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">普通攻击2</t>
   </si>
   <si>
-    <t xml:space="preserve">冰锥术</t>
+    <t xml:space="preserve">烈焰冲击</t>
   </si>
   <si>
     <t xml:space="preserve">发射一道可以在敌人之间弹射两次的冰锥，造成伤害并减速敌人10％。</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">湮灭黑洞</t>
   </si>
   <si>
-    <t xml:space="preserve">75|75|75|75|75</t>
+    <t xml:space="preserve">75|500</t>
   </si>
   <si>
     <t xml:space="preserve">在指定怪物身上种下雷核，持续牵引周围怪物5s并对周围所有敌人造成伤害。</t>
@@ -1809,18 +1809,20 @@
         <v>163644</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H24" s="13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="J24" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="K24" s="15"/>
+      <c r="K24" s="15" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">

--- a/diurenmw/Excels/SkillObj_技能表.xlsx
+++ b/diurenmw/Excels/SkillObj_技能表.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="104">
   <si>
     <t xml:space="preserve">int</t>
   </si>
@@ -572,28 +572,31 @@
     <t xml:space="preserve">发射一道可以在敌人之间弹射两次的冰锥，造成伤害并减速敌人10％。</t>
   </si>
   <si>
-    <t xml:space="preserve">火球术</t>
+    <t xml:space="preserve">凤凰冲击</t>
   </si>
   <si>
     <t xml:space="preserve">发射一枚火球，命中敌人时产生爆炸，造成伤害并击退敌人。</t>
   </si>
   <si>
-    <t xml:space="preserve">冰环术</t>
+    <t xml:space="preserve">三重闪电</t>
   </si>
   <si>
     <t xml:space="preserve">以自身为中心释放冰雪之力，冻结周围敌人并造成伤害。对精英以及BOSS效果降低。</t>
   </si>
   <si>
-    <t xml:space="preserve">暴风雪</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70|70|70</t>
+    <t xml:space="preserve">极冰盛宴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50|300</t>
   </si>
   <si>
     <t xml:space="preserve">改变指定地区环境，降下3s的暴风雪，对区域内敌人持续造成伤害并减速敌人。</t>
   </si>
   <si>
-    <t xml:space="preserve">闪电链</t>
+    <t xml:space="preserve">陨石降临</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200|500</t>
   </si>
   <si>
     <t xml:space="preserve">向敌人发射一道最多弹射6次的闪电链，优先弹射新敌人，僵直敌人并造成伤害。对同一敌人伤害递减20％。</t>
@@ -1847,15 +1850,17 @@
         <v>2</v>
       </c>
       <c r="H25" s="13" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I25" s="10" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="J25" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="K25" s="15"/>
+      <c r="K25" s="15" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
@@ -1888,7 +1893,9 @@
       <c r="J26" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="K26" s="15"/>
+      <c r="K26" s="15" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
@@ -1921,7 +1928,9 @@
       <c r="J27" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="K27" s="15"/>
+      <c r="K27" s="15" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
@@ -1948,20 +1957,22 @@
       <c r="H28" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="I28" s="10" t="n">
-        <v>200</v>
+      <c r="I28" s="10" t="s">
+        <v>74</v>
       </c>
       <c r="J28" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="K28" s="15"/>
+        <v>75</v>
+      </c>
+      <c r="K28" s="15" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="n">
         <v>2009</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C29" s="13" t="n">
         <v>1</v>
@@ -1982,10 +1993,10 @@
         <v>35</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J29" s="15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K29" s="15" t="s">
         <v>62</v>
@@ -1996,7 +2007,7 @@
         <v>2010</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C30" s="13" t="n">
         <v>1</v>
@@ -2020,7 +2031,7 @@
         <v>550</v>
       </c>
       <c r="J30" s="15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K30" s="15"/>
     </row>
@@ -2029,7 +2040,7 @@
         <v>2011</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C31" s="13" t="n">
         <v>1</v>
@@ -2050,10 +2061,10 @@
         <v>50</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J31" s="15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K31" s="15"/>
     </row>
@@ -2062,7 +2073,7 @@
         <v>2012</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C32" s="13" t="n">
         <v>1</v>
@@ -2083,7 +2094,7 @@
         <v>10</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K32" s="11"/>
     </row>
@@ -2092,7 +2103,7 @@
         <v>2013</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C33" s="13" t="n">
         <v>1</v>
@@ -2113,10 +2124,10 @@
         <v>80</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J33" s="15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K33" s="15"/>
     </row>
@@ -2125,7 +2136,7 @@
         <v>2014</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C34" s="13" t="n">
         <v>1</v>
@@ -2146,10 +2157,10 @@
         <v>60</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J34" s="15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K34" s="15"/>
     </row>
@@ -2158,7 +2169,7 @@
         <v>2015</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C35" s="13" t="n">
         <v>1</v>
@@ -2179,7 +2190,7 @@
         <v>60</v>
       </c>
       <c r="J35" s="15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K35" s="15"/>
     </row>
@@ -2193,7 +2204,7 @@
         <v>10001</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C37" s="13" t="n">
         <v>2</v>
@@ -2208,7 +2219,7 @@
         <v>163636</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K37" s="11"/>
     </row>
@@ -2217,7 +2228,7 @@
         <v>10002</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C38" s="13" t="n">
         <v>2</v>
@@ -2232,7 +2243,7 @@
         <v>143704</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K38" s="11"/>
     </row>
@@ -2241,7 +2252,7 @@
         <v>10003</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C39" s="13" t="n">
         <v>2</v>
@@ -2256,7 +2267,7 @@
         <v>145159</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K39" s="11"/>
     </row>
@@ -2265,7 +2276,7 @@
         <v>10004</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C40" s="13" t="n">
         <v>2</v>
@@ -2280,7 +2291,7 @@
         <v>163645</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K40" s="11"/>
     </row>
@@ -2289,7 +2300,7 @@
         <v>10005</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C41" s="13" t="n">
         <v>2</v>
@@ -2304,7 +2315,7 @@
         <v>143703</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K41" s="11"/>
     </row>

--- a/diurenmw/Excels/SkillObj_技能表.xlsx
+++ b/diurenmw/Excels/SkillObj_技能表.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="104">
   <si>
     <t xml:space="preserve">int</t>
   </si>
@@ -2004,7 +2004,7 @@
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="n">
-        <v>2010</v>
+        <v>2099</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>79</v>
@@ -2033,7 +2033,9 @@
       <c r="J30" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="K30" s="15"/>
+      <c r="K30" s="15" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="n">
